--- a/pm2018/pm2018.xlsx
+++ b/pm2018/pm2018.xlsx
@@ -580,7 +580,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="51.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="15.46"/>
@@ -673,7 +673,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -687,7 +687,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.91"/>
@@ -724,7 +724,7 @@
         <v>429</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>28</v>
@@ -744,7 +744,7 @@
         <v>394</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>32</v>
@@ -764,7 +764,7 @@
         <v>375</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>36</v>
@@ -804,7 +804,7 @@
         <v>365</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>44</v>
@@ -844,7 +844,7 @@
         <v>348</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>52</v>
@@ -864,7 +864,7 @@
         <v>341</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>56</v>
@@ -884,7 +884,7 @@
         <v>340</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>60</v>
@@ -904,7 +904,7 @@
         <v>318</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>64</v>
@@ -924,7 +924,7 @@
         <v>291</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>68</v>
@@ -944,7 +944,7 @@
         <v>287</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>72</v>
@@ -964,7 +964,7 @@
         <v>260</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>76</v>
@@ -984,7 +984,7 @@
         <v>191</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>80</v>
@@ -1004,7 +1004,7 @@
         <v>161</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>84</v>
@@ -1024,7 +1024,7 @@
         <v>160</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>88</v>
@@ -1044,7 +1044,7 @@
         <v>155</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>92</v>
@@ -1064,7 +1064,7 @@
         <v>154</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>96</v>
@@ -1084,7 +1084,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>100</v>
@@ -1104,7 +1104,7 @@
         <v>99</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>103</v>
@@ -1124,7 +1124,7 @@
         <v>94</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>107</v>
@@ -1144,7 +1144,7 @@
         <v>81</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>108</v>
@@ -1164,7 +1164,7 @@
         <v>75</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>112</v>
@@ -1184,7 +1184,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>116</v>
@@ -1204,7 +1204,7 @@
         <v>17</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>120</v>
@@ -1222,7 +1222,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
